--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT (#2) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -729,7 +729,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1824,7 +1824,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="89.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -732,7 +732,7 @@
     <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsElectronMicroscopyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
